--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N29_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N29_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>30.43800621299335</v>
+        <v>4.94617600961142</v>
       </c>
       <c r="D2" t="n">
-        <v>53.2024435529046</v>
+        <v>8.645397077346997</v>
       </c>
       <c r="E2" t="n">
-        <v>10.86061388180564</v>
+        <v>1.764849755793415</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6357232264436021</v>
+        <v>0.103305024297085</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.15923397660463</v>
+        <v>8.475875521198251</v>
       </c>
       <c r="D3" t="n">
-        <v>51.93099710001739</v>
+        <v>8.438787028752827</v>
       </c>
       <c r="E3" t="n">
-        <v>10.86061388180564</v>
+        <v>1.764849755793415</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6357232264436021</v>
+        <v>0.103305024297085</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
